--- a/ig/main/CodeSystem-TRE-R210-ActeSpecifique.xlsx
+++ b/ig/main/CodeSystem-TRE-R210-ActeSpecifique.xlsx
@@ -4927,7 +4927,7 @@
     <t>Activité physique adaptée</t>
   </si>
   <si>
-    <t xml:space="preserve">Permettre à une personne d'adopter un mode de vie physiquement actif de manière régulière, afin de réduire les facteurs de risque et les limitations fonctionnelles liés à une affection de longue durée, une maladie chronique ou une situation de perte d'autonomie. Elle s'adresse aux patients n'ayant pas un niveau régulier d'activité physique conforme aux recommandations de l'Organisation mondiale de la santé et qui ne peuvent augmenter leur niveau d'activité physique de manière autonome, adaptée et sécurisée. Les techniques utilisées relèvent des activités physiques et sportives et se distinguent des actes de rééducation réservés aux professionnels de santé, dans le respect de leurs compétences. </t>
+    <t>Permettre à une personne d'adopter un mode de vie physiquement actif de manière régulière, afin de réduire les facteurs de risque et les limitations fonctionnelles liés à une affection de longue durée, une maladie chronique ou une situation de perte d'autonomie. Elle s'adresse aux patients n'ayant pas un niveau régulier d'activité physique conforme aux recommandations de l'Organisation mondiale de la santé et qui ne peuvent augmenter leur niveau d'activité physique de manière autonome, adaptée et sécurisée. Les techniques utilisées relèvent des activités physiques et sportives et se distinguent des actes de rééducation réservés aux professionnels de santé, dans le respect de leurs compétences.</t>
   </si>
   <si>
     <t>0770</t>

--- a/ig/main/CodeSystem-TRE-R210-ActeSpecifique.xlsx
+++ b/ig/main/CodeSystem-TRE-R210-ActeSpecifique.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4830" uniqueCount="3290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4833" uniqueCount="3292">
   <si>
     <t>Property</t>
   </si>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-28T12:00:00+01:00</t>
+    <t>2025-04-25T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -9884,6 +9884,12 @@
   </si>
   <si>
     <t>Evaluation et accompagnement ergothérapique au positionnement au fauteuil roulant (MCPAA) et positionnement au lit</t>
+  </si>
+  <si>
+    <t>1511</t>
+  </si>
+  <si>
+    <t>Accompagnement précoce des déficiences</t>
   </si>
 </sst>
 </file>
@@ -10253,7 +10259,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D1510"/>
+  <dimension ref="A1:D1511"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -28880,6 +28886,18 @@
       </c>
       <c r="D1510" s="2"/>
     </row>
+    <row r="1511">
+      <c r="A1511" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B1511" t="s" s="2">
+        <v>3290</v>
+      </c>
+      <c r="C1511" t="s" s="2">
+        <v>3291</v>
+      </c>
+      <c r="D1511" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
